--- a/diseases/d003/2020-2025.xlsx
+++ b/diseases/d003/2020-2025.xlsx
@@ -1061,9 +1061,6 @@
       <c r="O4" t="n">
         <v>0</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="R4" t="n">
         <v>0</v>
       </c>
@@ -1457,9 +1454,6 @@
       <c r="O6" t="n">
         <v>0</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
         <v>0</v>
       </c>
@@ -2641,9 +2635,6 @@
       <c r="O14" t="n">
         <v>0</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="R14" t="n">
         <v>0</v>
       </c>
@@ -3677,9 +3668,6 @@
       <c r="O21" t="n">
         <v>0</v>
       </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
       <c r="R21" t="n">
         <v>0</v>
       </c>
@@ -4713,9 +4701,6 @@
       <c r="O28" t="n">
         <v>0</v>
       </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
       <c r="R28" t="n">
         <v>0</v>
       </c>
@@ -5897,9 +5882,6 @@
       <c r="O36" t="n">
         <v>0</v>
       </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
       <c r="R36" t="n">
         <v>0</v>
       </c>
@@ -6933,9 +6915,6 @@
       <c r="O43" t="n">
         <v>0</v>
       </c>
-      <c r="Q43" t="n">
-        <v>0</v>
-      </c>
       <c r="R43" t="n">
         <v>0</v>
       </c>
@@ -7969,9 +7948,6 @@
       <c r="O50" t="n">
         <v>0</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="R50" t="n">
         <v>0</v>
       </c>
@@ -9153,9 +9129,6 @@
       <c r="O58" t="n">
         <v>0</v>
       </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
       <c r="R58" t="n">
         <v>0</v>
       </c>
@@ -10189,9 +10162,6 @@
       <c r="O65" t="n">
         <v>0</v>
       </c>
-      <c r="Q65" t="n">
-        <v>0</v>
-      </c>
       <c r="R65" t="n">
         <v>0</v>
       </c>
@@ -11225,9 +11195,6 @@
       <c r="O72" t="n">
         <v>0</v>
       </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
       <c r="R72" t="n">
         <v>0</v>
       </c>
@@ -12409,9 +12376,6 @@
       <c r="O80" t="n">
         <v>0</v>
       </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
       <c r="R80" t="n">
         <v>0</v>
       </c>
@@ -13445,9 +13409,6 @@
       <c r="O87" t="n">
         <v>0</v>
       </c>
-      <c r="Q87" t="n">
-        <v>0</v>
-      </c>
       <c r="R87" t="n">
         <v>0</v>
       </c>
@@ -14481,9 +14442,6 @@
       <c r="O94" t="n">
         <v>0</v>
       </c>
-      <c r="Q94" t="n">
-        <v>0</v>
-      </c>
       <c r="R94" t="n">
         <v>0</v>
       </c>
@@ -15025,9 +14983,6 @@
       <c r="O97" t="n">
         <v>0</v>
       </c>
-      <c r="Q97" t="n">
-        <v>0</v>
-      </c>
       <c r="R97" t="n">
         <v>0</v>
       </c>
@@ -16061,9 +16016,6 @@
       <c r="O104" t="n">
         <v>0</v>
       </c>
-      <c r="Q104" t="n">
-        <v>0</v>
-      </c>
       <c r="R104" t="n">
         <v>0</v>
       </c>
@@ -17097,9 +17049,6 @@
       <c r="O111" t="n">
         <v>0</v>
       </c>
-      <c r="Q111" t="n">
-        <v>0</v>
-      </c>
       <c r="R111" t="n">
         <v>0</v>
       </c>
@@ -18133,9 +18082,6 @@
       <c r="O118" t="n">
         <v>0</v>
       </c>
-      <c r="Q118" t="n">
-        <v>0</v>
-      </c>
       <c r="R118" t="n">
         <v>0</v>
       </c>
@@ -19317,9 +19263,6 @@
       <c r="O126" t="n">
         <v>0</v>
       </c>
-      <c r="Q126" t="n">
-        <v>0</v>
-      </c>
       <c r="R126" t="n">
         <v>0</v>
       </c>
@@ -20353,9 +20296,6 @@
       <c r="O133" t="n">
         <v>0</v>
       </c>
-      <c r="Q133" t="n">
-        <v>0</v>
-      </c>
       <c r="R133" t="n">
         <v>0</v>
       </c>
@@ -21389,9 +21329,6 @@
       <c r="O140" t="n">
         <v>0</v>
       </c>
-      <c r="Q140" t="n">
-        <v>0</v>
-      </c>
       <c r="R140" t="n">
         <v>0</v>
       </c>
@@ -22573,9 +22510,6 @@
       <c r="O148" t="n">
         <v>0</v>
       </c>
-      <c r="Q148" t="n">
-        <v>0</v>
-      </c>
       <c r="R148" t="n">
         <v>0</v>
       </c>
@@ -23609,9 +23543,6 @@
       <c r="O155" t="n">
         <v>0</v>
       </c>
-      <c r="Q155" t="n">
-        <v>0</v>
-      </c>
       <c r="R155" t="n">
         <v>0</v>
       </c>
@@ -24793,9 +24724,6 @@
       <c r="O163" t="n">
         <v>0</v>
       </c>
-      <c r="Q163" t="n">
-        <v>0</v>
-      </c>
       <c r="R163" t="n">
         <v>0</v>
       </c>
@@ -25829,9 +25757,6 @@
       <c r="O170" t="n">
         <v>0</v>
       </c>
-      <c r="Q170" t="n">
-        <v>0</v>
-      </c>
       <c r="R170" t="n">
         <v>0</v>
       </c>
@@ -26865,9 +26790,6 @@
       <c r="O177" t="n">
         <v>0</v>
       </c>
-      <c r="Q177" t="n">
-        <v>0</v>
-      </c>
       <c r="R177" t="n">
         <v>0</v>
       </c>
@@ -28049,9 +27971,6 @@
       <c r="O185" t="n">
         <v>0</v>
       </c>
-      <c r="Q185" t="n">
-        <v>0</v>
-      </c>
       <c r="R185" t="n">
         <v>0</v>
       </c>
@@ -29085,9 +29004,6 @@
       <c r="O192" t="n">
         <v>0</v>
       </c>
-      <c r="Q192" t="n">
-        <v>0</v>
-      </c>
       <c r="R192" t="n">
         <v>0</v>
       </c>
@@ -30121,9 +30037,6 @@
       <c r="O199" t="n">
         <v>0</v>
       </c>
-      <c r="Q199" t="n">
-        <v>0</v>
-      </c>
       <c r="R199" t="n">
         <v>0</v>
       </c>
@@ -31305,9 +31218,6 @@
       <c r="O207" t="n">
         <v>0</v>
       </c>
-      <c r="Q207" t="n">
-        <v>0</v>
-      </c>
       <c r="R207" t="n">
         <v>0</v>
       </c>
@@ -32341,9 +32251,6 @@
       <c r="O214" t="n">
         <v>0</v>
       </c>
-      <c r="Q214" t="n">
-        <v>0</v>
-      </c>
       <c r="R214" t="n">
         <v>0</v>
       </c>
@@ -33377,9 +33284,6 @@
       <c r="O221" t="n">
         <v>0</v>
       </c>
-      <c r="Q221" t="n">
-        <v>0</v>
-      </c>
       <c r="R221" t="n">
         <v>0</v>
       </c>
@@ -34561,9 +34465,6 @@
       <c r="O229" t="n">
         <v>0</v>
       </c>
-      <c r="Q229" t="n">
-        <v>0</v>
-      </c>
       <c r="R229" t="n">
         <v>0</v>
       </c>
@@ -35597,9 +35498,6 @@
       <c r="O236" t="n">
         <v>0</v>
       </c>
-      <c r="Q236" t="n">
-        <v>0</v>
-      </c>
       <c r="R236" t="n">
         <v>0</v>
       </c>
@@ -36633,9 +36531,6 @@
       <c r="O243" t="n">
         <v>0</v>
       </c>
-      <c r="Q243" t="n">
-        <v>0</v>
-      </c>
       <c r="R243" t="n">
         <v>0</v>
       </c>
@@ -37817,9 +37712,6 @@
       <c r="O251" t="n">
         <v>0</v>
       </c>
-      <c r="Q251" t="n">
-        <v>0</v>
-      </c>
       <c r="R251" t="n">
         <v>0</v>
       </c>
@@ -38853,9 +38745,6 @@
       <c r="O258" t="n">
         <v>0</v>
       </c>
-      <c r="Q258" t="n">
-        <v>0</v>
-      </c>
       <c r="R258" t="n">
         <v>0</v>
       </c>
@@ -39889,9 +39778,6 @@
       <c r="O265" t="n">
         <v>0</v>
       </c>
-      <c r="Q265" t="n">
-        <v>0</v>
-      </c>
       <c r="R265" t="n">
         <v>0</v>
       </c>
@@ -41073,9 +40959,6 @@
       <c r="O273" t="n">
         <v>0</v>
       </c>
-      <c r="Q273" t="n">
-        <v>0</v>
-      </c>
       <c r="R273" t="n">
         <v>0</v>
       </c>
@@ -42109,9 +41992,6 @@
       <c r="O280" t="n">
         <v>0</v>
       </c>
-      <c r="Q280" t="n">
-        <v>0</v>
-      </c>
       <c r="R280" t="n">
         <v>0</v>
       </c>
@@ -43145,9 +43025,6 @@
       <c r="O287" t="n">
         <v>0</v>
       </c>
-      <c r="Q287" t="n">
-        <v>0</v>
-      </c>
       <c r="R287" t="n">
         <v>0</v>
       </c>
@@ -44329,9 +44206,6 @@
       <c r="O295" t="n">
         <v>0</v>
       </c>
-      <c r="Q295" t="n">
-        <v>0</v>
-      </c>
       <c r="R295" t="n">
         <v>0</v>
       </c>
@@ -45365,9 +45239,6 @@
       <c r="O302" t="n">
         <v>0</v>
       </c>
-      <c r="Q302" t="n">
-        <v>0</v>
-      </c>
       <c r="R302" t="n">
         <v>0</v>
       </c>
@@ -46401,9 +46272,6 @@
       <c r="O309" t="n">
         <v>0</v>
       </c>
-      <c r="Q309" t="n">
-        <v>0</v>
-      </c>
       <c r="R309" t="n">
         <v>0</v>
       </c>
@@ -47585,9 +47453,6 @@
       <c r="O317" t="n">
         <v>0</v>
       </c>
-      <c r="Q317" t="n">
-        <v>0</v>
-      </c>
       <c r="R317" t="n">
         <v>0</v>
       </c>
@@ -48621,9 +48486,6 @@
       <c r="O324" t="n">
         <v>0</v>
       </c>
-      <c r="Q324" t="n">
-        <v>0</v>
-      </c>
       <c r="R324" t="n">
         <v>0</v>
       </c>
@@ -49805,9 +49667,6 @@
       <c r="O332" t="n">
         <v>0</v>
       </c>
-      <c r="Q332" t="n">
-        <v>0</v>
-      </c>
       <c r="R332" t="n">
         <v>0</v>
       </c>
@@ -50841,9 +50700,6 @@
       <c r="O339" t="n">
         <v>0</v>
       </c>
-      <c r="Q339" t="n">
-        <v>0</v>
-      </c>
       <c r="R339" t="n">
         <v>0</v>
       </c>
@@ -51877,9 +51733,6 @@
       <c r="O346" t="n">
         <v>0</v>
       </c>
-      <c r="Q346" t="n">
-        <v>0</v>
-      </c>
       <c r="R346" t="n">
         <v>0</v>
       </c>
@@ -53061,9 +52914,6 @@
       <c r="O354" t="n">
         <v>0</v>
       </c>
-      <c r="Q354" t="n">
-        <v>0</v>
-      </c>
       <c r="R354" t="n">
         <v>0</v>
       </c>
@@ -54097,9 +53947,6 @@
       <c r="O361" t="n">
         <v>0</v>
       </c>
-      <c r="Q361" t="n">
-        <v>0</v>
-      </c>
       <c r="R361" t="n">
         <v>0</v>
       </c>
@@ -55133,9 +54980,6 @@
       <c r="O368" t="n">
         <v>0</v>
       </c>
-      <c r="Q368" t="n">
-        <v>0</v>
-      </c>
       <c r="R368" t="n">
         <v>0</v>
       </c>
@@ -56317,9 +56161,6 @@
       <c r="O376" t="n">
         <v>0</v>
       </c>
-      <c r="Q376" t="n">
-        <v>0</v>
-      </c>
       <c r="R376" t="n">
         <v>0</v>
       </c>
@@ -57353,9 +57194,6 @@
       <c r="O383" t="n">
         <v>0</v>
       </c>
-      <c r="Q383" t="n">
-        <v>0</v>
-      </c>
       <c r="R383" t="n">
         <v>0</v>
       </c>
@@ -58389,9 +58227,6 @@
       <c r="O390" t="n">
         <v>0</v>
       </c>
-      <c r="Q390" t="n">
-        <v>0</v>
-      </c>
       <c r="R390" t="n">
         <v>0</v>
       </c>
@@ -59573,9 +59408,6 @@
       <c r="O398" t="n">
         <v>0</v>
       </c>
-      <c r="Q398" t="n">
-        <v>0</v>
-      </c>
       <c r="R398" t="n">
         <v>0</v>
       </c>
@@ -60609,9 +60441,6 @@
       <c r="O405" t="n">
         <v>0</v>
       </c>
-      <c r="Q405" t="n">
-        <v>0</v>
-      </c>
       <c r="R405" t="n">
         <v>0</v>
       </c>
@@ -61645,9 +61474,6 @@
       <c r="O412" t="n">
         <v>0</v>
       </c>
-      <c r="Q412" t="n">
-        <v>0</v>
-      </c>
       <c r="R412" t="n">
         <v>0</v>
       </c>
@@ -62829,9 +62655,6 @@
       <c r="O420" t="n">
         <v>0</v>
       </c>
-      <c r="Q420" t="n">
-        <v>0</v>
-      </c>
       <c r="R420" t="n">
         <v>0</v>
       </c>
@@ -63865,9 +63688,6 @@
       <c r="O427" t="n">
         <v>0</v>
       </c>
-      <c r="Q427" t="n">
-        <v>0</v>
-      </c>
       <c r="R427" t="n">
         <v>0</v>
       </c>
@@ -65049,9 +64869,6 @@
       <c r="O435" t="n">
         <v>0</v>
       </c>
-      <c r="Q435" t="n">
-        <v>0</v>
-      </c>
       <c r="R435" t="n">
         <v>0</v>
       </c>
@@ -66085,9 +65902,6 @@
       <c r="O442" t="n">
         <v>0</v>
       </c>
-      <c r="Q442" t="n">
-        <v>0</v>
-      </c>
       <c r="R442" t="n">
         <v>0</v>
       </c>
@@ -67121,9 +66935,6 @@
       <c r="O449" t="n">
         <v>0</v>
       </c>
-      <c r="Q449" t="n">
-        <v>0</v>
-      </c>
       <c r="R449" t="n">
         <v>0</v>
       </c>
@@ -68305,9 +68116,6 @@
       <c r="O457" t="n">
         <v>0</v>
       </c>
-      <c r="Q457" t="n">
-        <v>0</v>
-      </c>
       <c r="R457" t="n">
         <v>0</v>
       </c>
@@ -69341,9 +69149,6 @@
       <c r="O464" t="n">
         <v>0</v>
       </c>
-      <c r="Q464" t="n">
-        <v>0</v>
-      </c>
       <c r="R464" t="n">
         <v>0</v>
       </c>
@@ -70377,9 +70182,6 @@
       <c r="O471" t="n">
         <v>0</v>
       </c>
-      <c r="Q471" t="n">
-        <v>0</v>
-      </c>
       <c r="R471" t="n">
         <v>0</v>
       </c>
@@ -71413,9 +71215,6 @@
       <c r="O478" t="n">
         <v>0</v>
       </c>
-      <c r="Q478" t="n">
-        <v>0</v>
-      </c>
       <c r="R478" t="n">
         <v>0</v>
       </c>
@@ -72597,9 +72396,6 @@
       <c r="O486" t="n">
         <v>0</v>
       </c>
-      <c r="Q486" t="n">
-        <v>0</v>
-      </c>
       <c r="R486" t="n">
         <v>0</v>
       </c>
@@ -73633,9 +73429,6 @@
       <c r="O493" t="n">
         <v>0</v>
       </c>
-      <c r="Q493" t="n">
-        <v>0</v>
-      </c>
       <c r="R493" t="n">
         <v>0</v>
       </c>
@@ -74817,9 +74610,6 @@
       <c r="O501" t="n">
         <v>0</v>
       </c>
-      <c r="Q501" t="n">
-        <v>0</v>
-      </c>
       <c r="R501" t="n">
         <v>0</v>
       </c>
@@ -75853,9 +75643,6 @@
       <c r="O508" t="n">
         <v>0</v>
       </c>
-      <c r="Q508" t="n">
-        <v>0</v>
-      </c>
       <c r="R508" t="n">
         <v>0</v>
       </c>
@@ -76889,9 +76676,6 @@
       <c r="O515" t="n">
         <v>0</v>
       </c>
-      <c r="Q515" t="n">
-        <v>0</v>
-      </c>
       <c r="R515" t="n">
         <v>0</v>
       </c>
@@ -78073,9 +77857,6 @@
       <c r="O523" t="n">
         <v>0</v>
       </c>
-      <c r="Q523" t="n">
-        <v>0</v>
-      </c>
       <c r="R523" t="n">
         <v>0</v>
       </c>
@@ -79107,9 +78888,6 @@
         <v>0</v>
       </c>
       <c r="O530" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q530" t="n">
         <v>0</v>
       </c>
       <c r="R530" t="n">
